--- a/docs/reference/grounding/snomed_eval.xlsx
+++ b/docs/reference/grounding/snomed_eval.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emrecalik/Desktop/doktorarbeit/CGG_evaluation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A8D2E56-D73B-6845-A6EC-710B0E0C62B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6BA342-90C4-FE49-86FF-156E0B6FC40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" xr2:uid="{69C25FA0-E741-2346-8F77-8B487E080EF2}"/>
+    <workbookView xWindow="30400" yWindow="660" windowWidth="50880" windowHeight="27980" xr2:uid="{69C25FA0-E741-2346-8F77-8B487E080EF2}"/>
   </bookViews>
   <sheets>
     <sheet name="snomed eval" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="160">
   <si>
     <t>wrong match</t>
   </si>
@@ -95,9 +95,6 @@
     <t>t0_row_01</t>
   </si>
   <si>
-    <t>RECHECK GOLD STANDARD</t>
-  </si>
-  <si>
     <t xml:space="preserve">too general </t>
   </si>
   <si>
@@ -318,12 +315,6 @@
   </si>
   <si>
     <t>Proton pump inhibitor</t>
-  </si>
-  <si>
-    <t>ERROR?</t>
-  </si>
-  <si>
-    <t>ERROR</t>
   </si>
   <si>
     <t>Repair of coronary artery (procedure)</t>
@@ -531,7 +522,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -562,20 +553,13 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF3F3F76"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -590,11 +574,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -672,37 +651,33 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="5"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="5" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="5" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="4"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="5" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="3"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="4" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="20% - Accent1" xfId="5" builtinId="30"/>
+  <cellStyles count="5">
+    <cellStyle name="20% - Accent1" xfId="4" builtinId="30"/>
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
-    <cellStyle name="Input" xfId="4" builtinId="20"/>
-    <cellStyle name="Neutral" xfId="3" builtinId="28"/>
+    <cellStyle name="Input" xfId="3" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -1093,75 +1068,75 @@
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="K1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="L1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="12">
+      <c r="A2" s="10">
         <v>22</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="F2" s="12">
+      <c r="E2" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="10">
         <v>233817007</v>
       </c>
-      <c r="G2" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="G2" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H2" s="10">
         <v>233817007</v>
       </c>
-      <c r="I2" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="J2" s="12">
-        <v>1</v>
-      </c>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10">
+      <c r="I2" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="J2" s="10">
+        <v>1</v>
+      </c>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8">
         <v>1</v>
       </c>
       <c r="M2"/>
@@ -1187,146 +1162,146 @@
       <c r="AG2"/>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A3" s="11">
+      <c r="A3" s="9">
         <v>28</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="F3" s="11">
+      <c r="E3" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F3" s="9">
         <v>698805004</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="H3" s="11">
+      <c r="G3" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="H3" s="9">
         <v>698805004</v>
       </c>
-      <c r="I3" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="J3" s="11">
-        <v>1</v>
-      </c>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10">
+      <c r="I3" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="J3" s="9">
+        <v>1</v>
+      </c>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>42</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="C4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="F4" s="11">
+      <c r="E4" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F4" s="9">
         <v>698805004</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="H4" s="11">
+      <c r="G4" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="H4" s="9">
         <v>698805004</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="J4" s="11">
-        <v>1</v>
-      </c>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10">
+      <c r="I4" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="J4" s="9">
+        <v>1</v>
+      </c>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A5" s="11">
+      <c r="A5" s="9">
         <v>45</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="F5" s="11">
+      <c r="E5" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F5" s="9">
         <v>698805004</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="H5" s="11">
+      <c r="G5" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="H5" s="9">
         <v>698805004</v>
       </c>
-      <c r="I5" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="J5" s="11">
-        <v>1</v>
-      </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="12">
+      <c r="I5" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="J5" s="9">
+        <v>1</v>
+      </c>
+      <c r="K5" s="10"/>
+      <c r="L5" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="10">
         <v>78</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F6" s="10">
+      <c r="E6" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="F6" s="8">
         <v>698805004</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="H6" s="10">
+      <c r="G6" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H6" s="8">
         <v>698805004</v>
       </c>
-      <c r="I6" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="J6" s="10">
-        <v>1</v>
-      </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10">
+      <c r="I6" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="J6" s="8">
+        <v>1</v>
+      </c>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8">
         <v>1</v>
       </c>
       <c r="M6"/>
@@ -1352,182 +1327,182 @@
       <c r="AG6"/>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A7" s="11">
+      <c r="A7" s="9">
         <v>51</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="11" t="s">
+      <c r="C7" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="F7" s="11">
+      <c r="E7" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F7" s="9">
         <v>876857001</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="H7" s="11">
+      <c r="G7" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H7" s="9">
         <v>876857001</v>
       </c>
-      <c r="I7" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="J7" s="11">
-        <v>1</v>
-      </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10">
+      <c r="I7" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="J7" s="9">
+        <v>1</v>
+      </c>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A8" s="10">
+      <c r="A8" s="8">
         <v>39</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="11" t="s">
+      <c r="C8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="F8" s="11">
+      <c r="E8" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F8" s="9">
         <v>194842008</v>
       </c>
-      <c r="G8" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H8" s="11">
+      <c r="G8" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="H8" s="9">
         <v>194842008</v>
       </c>
-      <c r="I8" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="J8" s="11">
-        <v>1</v>
-      </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10">
+      <c r="I8" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="J8" s="9">
+        <v>1</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A9" s="11">
+      <c r="A9" s="9">
         <v>3</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="F9" s="11">
+      <c r="E9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F9" s="9">
         <v>442031002</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="H9" s="11">
+      <c r="G9" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="H9" s="9">
         <v>442031002</v>
       </c>
-      <c r="I9" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="J9" s="11">
-        <v>1</v>
-      </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10">
+      <c r="I9" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="J9" s="9">
+        <v>1</v>
+      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A10" s="12">
+      <c r="A10" s="10">
         <v>97</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="11" t="s">
+      <c r="B10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="F10" s="11">
+      <c r="E10" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F10" s="9">
         <v>442031002</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="H10" s="11">
+      <c r="G10" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="H10" s="9">
         <v>442031002</v>
       </c>
-      <c r="I10" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="J10" s="11">
-        <v>1</v>
-      </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10">
+      <c r="I10" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="J10" s="9">
+        <v>1</v>
+      </c>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="11">
+      <c r="A11" s="9">
         <v>27</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="F11" s="10">
+      <c r="E11" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F11" s="8">
         <v>443129001</v>
       </c>
-      <c r="G11" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="H11" s="10">
+      <c r="G11" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H11" s="8">
         <v>443129001</v>
       </c>
-      <c r="I11" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="J11" s="10">
-        <v>1</v>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10">
+      <c r="I11" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J11" s="8">
+        <v>1</v>
+      </c>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8">
         <v>1</v>
       </c>
       <c r="M11"/>
@@ -1553,74 +1528,74 @@
       <c r="AG11"/>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A12" s="12">
+      <c r="A12" s="10">
         <v>77</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="11" t="s">
+      <c r="B12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="F12" s="11">
+      <c r="E12" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="F12" s="9">
         <v>443129001</v>
       </c>
-      <c r="G12" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="H12" s="11">
+      <c r="G12" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="H12" s="9">
         <v>443129001</v>
       </c>
-      <c r="I12" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="J12" s="11">
-        <v>1</v>
-      </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="11">
+      <c r="I12" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="J12" s="9">
+        <v>1</v>
+      </c>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="9">
         <v>83</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="F13" s="14">
+      <c r="B13" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" s="12">
         <v>36969009</v>
       </c>
-      <c r="G13" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="H13" s="14">
+      <c r="G13" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="H13" s="12">
         <v>36969009</v>
       </c>
-      <c r="I13" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="J13" s="14">
-        <v>1</v>
-      </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="10">
+      <c r="I13" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="J13" s="12">
+        <v>1</v>
+      </c>
+      <c r="K13" s="12"/>
+      <c r="L13" s="8">
         <v>1</v>
       </c>
       <c r="M13"/>
@@ -1646,109 +1621,109 @@
       <c r="AG13"/>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A14" s="12">
+      <c r="A14" s="10">
         <v>11</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="12" t="s">
+      <c r="C14" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="F14" s="12">
+      <c r="E14" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="F14" s="10">
         <v>840580004</v>
       </c>
-      <c r="G14" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="H14" s="12">
+      <c r="G14" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="H14" s="10">
         <v>840580004</v>
       </c>
-      <c r="I14" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="J14" s="12">
-        <v>1</v>
-      </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10">
+      <c r="I14" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="J14" s="10">
+        <v>1</v>
+      </c>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A15" s="11">
+      <c r="A15" s="9">
         <v>47</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="F15" s="10">
+      <c r="D15" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="F15" s="8">
         <v>392010000</v>
       </c>
-      <c r="G15" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="H15" s="10">
+      <c r="G15" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="H15" s="8">
         <v>392010000</v>
       </c>
-      <c r="I15" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="J15" s="10">
-        <v>1</v>
-      </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="10">
+      <c r="I15" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="J15" s="8">
+        <v>1</v>
+      </c>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="8">
         <v>9</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="12" t="s">
+      <c r="C16" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="F16" s="12">
+      <c r="E16" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F16" s="10">
         <v>414795007</v>
       </c>
-      <c r="G16" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="H16" s="12">
+      <c r="G16" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H16" s="10">
         <v>414795007</v>
       </c>
-      <c r="I16" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="J16" s="12">
-        <v>1</v>
-      </c>
-      <c r="L16" s="10">
+      <c r="I16" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="J16" s="10">
+        <v>1</v>
+      </c>
+      <c r="L16" s="8">
         <v>1</v>
       </c>
       <c r="M16"/>
@@ -1773,38 +1748,38 @@
       <c r="AF16"/>
       <c r="AG16"/>
     </row>
-    <row r="17" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11">
+    <row r="17" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="9">
         <v>38</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="10" t="s">
+      <c r="C17" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F17" s="10">
+      <c r="E17" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F17" s="8">
         <v>414795007</v>
       </c>
-      <c r="G17" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="H17" s="10">
+      <c r="G17" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="H17" s="8">
         <v>414795007</v>
       </c>
-      <c r="I17" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="J17" s="10">
-        <v>1</v>
-      </c>
-      <c r="L17" s="10">
+      <c r="I17" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="J17" s="8">
+        <v>1</v>
+      </c>
+      <c r="L17" s="8">
         <v>1</v>
       </c>
       <c r="M17"/>
@@ -1830,73 +1805,73 @@
       <c r="AG17"/>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A18" s="12">
+      <c r="A18" s="10">
         <v>73</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="10" t="s">
+      <c r="B18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F18" s="10">
+      <c r="E18" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F18" s="8">
         <v>414795007</v>
       </c>
-      <c r="G18" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="H18" s="10">
+      <c r="G18" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="H18" s="8">
         <v>414795007</v>
       </c>
-      <c r="I18" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="J18" s="10">
-        <v>1</v>
-      </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="11">
+      <c r="I18" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="J18" s="8">
+        <v>1</v>
+      </c>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="9">
         <v>16</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F19" s="10">
+      <c r="D19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" s="8">
         <v>243121000</v>
       </c>
-      <c r="G19" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="H19" s="10">
+      <c r="G19" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H19" s="8">
         <v>243121000</v>
       </c>
-      <c r="I19" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="J19" s="10">
-        <v>1</v>
-      </c>
-      <c r="L19" s="10">
+      <c r="I19" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="J19" s="8">
+        <v>1</v>
+      </c>
+      <c r="L19" s="8">
         <v>1</v>
       </c>
       <c r="M19"/>
@@ -1921,38 +1896,38 @@
       <c r="AF19"/>
       <c r="AG19"/>
     </row>
-    <row r="20" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12">
+    <row r="20" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="10">
         <v>29</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F20" s="10">
+      <c r="D20" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" s="8">
         <v>243121000</v>
       </c>
-      <c r="G20" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="H20" s="10">
+      <c r="G20" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H20" s="8">
         <v>243121000</v>
       </c>
-      <c r="I20" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="J20" s="10">
-        <v>1</v>
-      </c>
-      <c r="L20" s="10">
+      <c r="I20" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="J20" s="8">
+        <v>1</v>
+      </c>
+      <c r="L20" s="8">
         <v>1</v>
       </c>
       <c r="M20"/>
@@ -1978,109 +1953,109 @@
       <c r="AG20"/>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A21" s="11">
+      <c r="A21" s="9">
         <v>23</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="F21" s="10">
+      <c r="C21" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="8">
         <v>250908004</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" s="8">
+        <v>250908004</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J21" s="8">
+        <v>1</v>
+      </c>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A22" s="10">
+        <v>40</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="H21" s="10">
+      <c r="F22" s="8">
         <v>250908004</v>
       </c>
-      <c r="I21" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J21" s="10">
-        <v>1</v>
-      </c>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A22" s="12">
-        <v>40</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="F22" s="10">
+      <c r="G22" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H22" s="8">
         <v>250908004</v>
       </c>
-      <c r="G22" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="H22" s="10">
-        <v>250908004</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J22" s="10">
-        <v>1</v>
-      </c>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="11">
+      <c r="I22" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J22" s="8">
+        <v>1</v>
+      </c>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="9">
         <v>103</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="10" t="s">
+      <c r="B23" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="F23" s="10">
+      <c r="E23" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F23" s="8">
         <v>422504002</v>
       </c>
-      <c r="G23" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="H23" s="10">
+      <c r="G23" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H23" s="8">
         <v>422504002</v>
       </c>
-      <c r="I23" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="J23" s="10">
-        <v>1</v>
-      </c>
-      <c r="L23" s="10">
+      <c r="I23" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="J23" s="8">
+        <v>1</v>
+      </c>
+      <c r="L23" s="8">
         <v>1</v>
       </c>
       <c r="M23"/>
@@ -2105,38 +2080,38 @@
       <c r="AF23"/>
       <c r="AG23"/>
     </row>
-    <row r="24" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12">
+    <row r="24" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="10">
         <v>46</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="F24" s="10">
+      <c r="D24" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="8">
         <v>241467003</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="H24" s="10">
+      <c r="G24" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="H24" s="8">
         <v>241467003</v>
       </c>
-      <c r="I24" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="J24" s="10">
-        <v>1</v>
-      </c>
-      <c r="L24" s="10">
+      <c r="I24" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="J24" s="8">
+        <v>1</v>
+      </c>
+      <c r="L24" s="8">
         <v>1</v>
       </c>
       <c r="M24"/>
@@ -2162,145 +2137,145 @@
       <c r="AG24"/>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A25" s="11">
+      <c r="A25" s="9">
         <v>4</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="F25" s="12">
+      <c r="D25" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F25" s="10">
         <v>310866003</v>
       </c>
-      <c r="G25" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="H25" s="12">
+      <c r="G25" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="H25" s="10">
         <v>310866003</v>
       </c>
-      <c r="I25" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="J25" s="12">
-        <v>1</v>
-      </c>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10">
+      <c r="I25" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="J25" s="10">
+        <v>1</v>
+      </c>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A26" s="12">
+      <c r="A26" s="10">
         <v>106</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="10" t="s">
+      <c r="B26" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E26" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F26" s="10">
+      <c r="E26" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F26" s="8">
         <v>419847008</v>
       </c>
-      <c r="G26" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="H26" s="10">
+      <c r="G26" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="H26" s="8">
         <v>419847008</v>
       </c>
-      <c r="I26" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="J26" s="10">
-        <v>1</v>
-      </c>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10">
+      <c r="I26" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="J26" s="8">
+        <v>1</v>
+      </c>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A27" s="11">
+      <c r="A27" s="9">
         <v>112</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="10" t="s">
+      <c r="B27" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F27" s="10">
+      <c r="E27" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F27" s="8">
         <v>419847008</v>
       </c>
-      <c r="G27" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="H27" s="10">
+      <c r="G27" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="H27" s="8">
         <v>419847008</v>
       </c>
-      <c r="I27" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="J27" s="10">
-        <v>1</v>
-      </c>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="12">
+      <c r="I27" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="J27" s="8">
+        <v>1</v>
+      </c>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="10">
         <v>8</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="12" t="s">
+      <c r="C28" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E28" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F28" s="12">
+      <c r="E28" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" s="10">
         <v>1255670000</v>
       </c>
-      <c r="G28" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H28" s="12">
+      <c r="G28" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H28" s="10">
         <v>1255670000</v>
       </c>
-      <c r="I28" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J28" s="12">
-        <v>1</v>
-      </c>
-      <c r="L28" s="10">
+      <c r="I28" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J28" s="10">
+        <v>1</v>
+      </c>
+      <c r="L28" s="8">
         <v>1</v>
       </c>
       <c r="M28"/>
@@ -2325,38 +2300,38 @@
       <c r="AF28"/>
       <c r="AG28"/>
     </row>
-    <row r="29" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="11">
+    <row r="29" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="9">
         <v>36</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="10" t="s">
+      <c r="C29" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F29" s="10">
+      <c r="E29" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="8">
         <v>1255670000</v>
       </c>
-      <c r="G29" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H29" s="10">
+      <c r="G29" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H29" s="8">
         <v>1255670000</v>
       </c>
-      <c r="I29" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="J29" s="10">
-        <v>1</v>
-      </c>
-      <c r="L29" s="10">
+      <c r="I29" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J29" s="8">
+        <v>1</v>
+      </c>
+      <c r="L29" s="8">
         <v>1</v>
       </c>
       <c r="M29"/>
@@ -2381,38 +2356,38 @@
       <c r="AF29"/>
       <c r="AG29"/>
     </row>
-    <row r="30" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="10">
+    <row r="30" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
         <v>71</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="10" t="s">
+      <c r="B30" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E30" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F30" s="10">
+      <c r="E30" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F30" s="8">
         <v>1255670000</v>
       </c>
-      <c r="G30" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H30" s="10">
+      <c r="G30" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H30" s="8">
         <v>1255670000</v>
       </c>
-      <c r="I30" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="J30" s="10">
-        <v>1</v>
-      </c>
-      <c r="L30" s="10">
+      <c r="I30" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J30" s="8">
+        <v>1</v>
+      </c>
+      <c r="L30" s="8">
         <v>1</v>
       </c>
       <c r="M30"/>
@@ -2438,109 +2413,109 @@
       <c r="AG30"/>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A31" s="11">
+      <c r="A31" s="9">
         <v>101</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="10" t="s">
+      <c r="B31" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F31" s="10">
+      <c r="E31" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F31" s="8">
         <v>1255670000</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H31" s="8">
+        <v>1255670000</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J31" s="8">
+        <v>1</v>
+      </c>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>119</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H31" s="10">
+      <c r="F32" s="8">
         <v>1255670000</v>
       </c>
-      <c r="I31" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="J31" s="10">
-        <v>1</v>
-      </c>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A32" s="12">
-        <v>119</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F32" s="10">
+      <c r="G32" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H32" s="8">
         <v>1255670000</v>
       </c>
-      <c r="G32" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H32" s="10">
-        <v>1255670000</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="J32" s="10">
-        <v>1</v>
-      </c>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="11">
+      <c r="I32" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J32" s="8">
+        <v>1</v>
+      </c>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="9">
         <v>35</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="10" t="s">
+      <c r="C33" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E33" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="F33" s="10">
+      <c r="E33" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F33" s="8">
         <v>194843003</v>
       </c>
-      <c r="G33" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H33" s="10">
+      <c r="G33" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="H33" s="8">
         <v>194843003</v>
       </c>
-      <c r="I33" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="J33" s="10">
-        <v>1</v>
-      </c>
-      <c r="L33" s="10">
+      <c r="I33" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="J33" s="8">
+        <v>1</v>
+      </c>
+      <c r="L33" s="8">
         <v>1</v>
       </c>
       <c r="M33"/>
@@ -2566,73 +2541,73 @@
       <c r="AG33"/>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A34" s="12">
+      <c r="A34" s="10">
         <v>100</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" s="10" t="s">
+      <c r="B34" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F34" s="10">
+      <c r="E34" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F34" s="8">
         <v>421327009</v>
       </c>
-      <c r="G34" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="H34" s="10">
+      <c r="G34" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="H34" s="8">
         <v>421327009</v>
       </c>
-      <c r="I34" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="J34" s="10">
-        <v>1</v>
-      </c>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="11">
+      <c r="I34" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J34" s="8">
+        <v>1</v>
+      </c>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="9">
         <v>7</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" s="12" t="s">
+      <c r="C35" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E35" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F35" s="12">
+      <c r="E35" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F35" s="10">
         <v>53741008</v>
       </c>
-      <c r="G35" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="H35" s="12">
+      <c r="G35" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H35" s="10">
         <v>53741008</v>
       </c>
-      <c r="I35" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="J35" s="12">
-        <v>1</v>
-      </c>
-      <c r="L35" s="10">
+      <c r="I35" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="J35" s="10">
+        <v>1</v>
+      </c>
+      <c r="L35" s="8">
         <v>1</v>
       </c>
       <c r="M35"/>
@@ -2657,39 +2632,39 @@
       <c r="AF35"/>
       <c r="AG35"/>
     </row>
-    <row r="36" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="12">
+    <row r="36" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
         <v>19</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="12" t="s">
+      <c r="C36" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E36" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F36" s="12">
+      <c r="E36" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F36" s="10">
         <v>53741008</v>
       </c>
-      <c r="G36" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="H36" s="12">
+      <c r="G36" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H36" s="10">
         <v>53741008</v>
       </c>
-      <c r="I36" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="J36" s="12">
-        <v>1</v>
-      </c>
-      <c r="K36" s="12"/>
-      <c r="L36" s="10">
+      <c r="I36" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="J36" s="10">
+        <v>1</v>
+      </c>
+      <c r="K36" s="10"/>
+      <c r="L36" s="8">
         <v>1</v>
       </c>
       <c r="M36"/>
@@ -2714,38 +2689,38 @@
       <c r="AF36"/>
       <c r="AG36"/>
     </row>
-    <row r="37" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="11">
+    <row r="37" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
         <v>116</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="F37" s="10">
+      <c r="C37" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F37" s="8">
         <v>232717009</v>
       </c>
-      <c r="G37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H37" s="10">
+      <c r="G37" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H37" s="8">
         <v>232717009</v>
       </c>
-      <c r="I37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J37" s="10">
-        <v>1</v>
-      </c>
-      <c r="L37" s="10">
+      <c r="I37" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J37" s="8">
+        <v>1</v>
+      </c>
+      <c r="L37" s="8">
         <v>1</v>
       </c>
       <c r="M37"/>
@@ -2771,73 +2746,73 @@
       <c r="AG37"/>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A38" s="12">
+      <c r="A38" s="10">
         <v>2</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="F38" s="12">
+      <c r="E38" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F38" s="10">
         <v>386952008</v>
       </c>
-      <c r="G38" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="H38" s="12">
+      <c r="G38" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H38" s="10">
         <v>386952008</v>
       </c>
-      <c r="I38" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="J38" s="12">
-        <v>1</v>
-      </c>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="11">
+      <c r="I38" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="J38" s="10">
+        <v>1</v>
+      </c>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="9">
         <v>15</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="F39" s="12">
+      <c r="E39" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F39" s="10">
         <v>386952008</v>
       </c>
-      <c r="G39" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="H39" s="12">
+      <c r="G39" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H39" s="10">
         <v>386952008</v>
       </c>
-      <c r="I39" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="J39" s="12">
-        <v>1</v>
-      </c>
-      <c r="L39" s="10">
+      <c r="I39" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="J39" s="10">
+        <v>1</v>
+      </c>
+      <c r="L39" s="8">
         <v>1</v>
       </c>
       <c r="M39"/>
@@ -2862,38 +2837,38 @@
       <c r="AF39"/>
       <c r="AG39"/>
     </row>
-    <row r="40" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="12">
+    <row r="40" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="10">
         <v>90</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="F40" s="10">
+      <c r="E40" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F40" s="8">
         <v>386952008</v>
       </c>
-      <c r="G40" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="H40" s="10">
+      <c r="G40" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="H40" s="8">
         <v>386952008</v>
       </c>
-      <c r="I40" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="J40" s="10">
-        <v>1</v>
-      </c>
-      <c r="L40" s="10">
+      <c r="I40" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="J40" s="8">
+        <v>1</v>
+      </c>
+      <c r="L40" s="8">
         <v>1</v>
       </c>
       <c r="M40"/>
@@ -2918,38 +2893,38 @@
       <c r="AF40"/>
       <c r="AG40"/>
     </row>
-    <row r="41" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="11">
+    <row r="41" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="9">
         <v>6</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" s="12" t="s">
+      <c r="C41" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E41" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="F41" s="12">
+      <c r="E41" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F41" s="10">
         <v>413838009</v>
       </c>
-      <c r="G41" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="H41" s="12">
+      <c r="G41" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="H41" s="10">
         <v>413838009</v>
       </c>
-      <c r="I41" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="J41" s="12">
-        <v>1</v>
-      </c>
-      <c r="L41" s="10">
+      <c r="I41" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="J41" s="10">
+        <v>1</v>
+      </c>
+      <c r="L41" s="8">
         <v>1</v>
       </c>
       <c r="M41"/>
@@ -2975,73 +2950,73 @@
       <c r="AG41"/>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A42" s="12">
+      <c r="A42" s="10">
         <v>18</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C42" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42" s="12" t="s">
+      <c r="C42" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E42" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="F42" s="12">
+      <c r="E42" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F42" s="10">
         <v>413838009</v>
       </c>
-      <c r="G42" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="H42" s="12">
+      <c r="G42" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="H42" s="10">
         <v>413838009</v>
       </c>
-      <c r="I42" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="J42" s="12">
-        <v>1</v>
-      </c>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="11">
+      <c r="I42" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="J42" s="10">
+        <v>1</v>
+      </c>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="9">
         <v>34</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D43" s="10" t="s">
+      <c r="C43" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E43" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F43" s="10">
+      <c r="E43" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F43" s="8">
         <v>413838009</v>
       </c>
-      <c r="G43" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="H43" s="10">
+      <c r="G43" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H43" s="8">
         <v>413838009</v>
       </c>
-      <c r="I43" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J43" s="10">
-        <v>1</v>
-      </c>
-      <c r="L43" s="10">
+      <c r="I43" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J43" s="8">
+        <v>1</v>
+      </c>
+      <c r="L43" s="8">
         <v>1</v>
       </c>
       <c r="M43"/>
@@ -3067,109 +3042,109 @@
       <c r="AG43"/>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A44" s="12">
+      <c r="A44" s="10">
         <v>48</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44" s="10" t="s">
+      <c r="C44" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E44" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F44" s="10">
+      <c r="E44" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F44" s="8">
         <v>413838009</v>
       </c>
-      <c r="G44" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="H44" s="10">
+      <c r="G44" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H44" s="8">
         <v>413838009</v>
       </c>
-      <c r="I44" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J44" s="10">
-        <v>1</v>
-      </c>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10">
+      <c r="I44" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J44" s="8">
+        <v>1</v>
+      </c>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A45" s="11">
+      <c r="A45" s="9">
         <v>56</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F45" s="8">
+        <v>413838009</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H45" s="8">
+        <v>413838009</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J45" s="8">
+        <v>1</v>
+      </c>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="10">
         <v>60</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D45" s="10" t="s">
+      <c r="B46" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E45" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F45" s="10">
+      <c r="E46" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F46" s="8">
         <v>413838009</v>
       </c>
-      <c r="G45" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="H45" s="10">
+      <c r="G46" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H46" s="8">
         <v>413838009</v>
       </c>
-      <c r="I45" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J45" s="10">
-        <v>1</v>
-      </c>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="12">
-        <v>60</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F46" s="10">
-        <v>413838009</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="H46" s="10">
-        <v>413838009</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J46" s="10">
-        <v>1</v>
-      </c>
-      <c r="L46" s="10">
+      <c r="I46" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J46" s="8">
+        <v>1</v>
+      </c>
+      <c r="L46" s="8">
         <v>1</v>
       </c>
       <c r="M46"/>
@@ -3194,38 +3169,38 @@
       <c r="AF46"/>
       <c r="AG46"/>
     </row>
-    <row r="47" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="11">
+    <row r="47" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="9">
         <v>70</v>
       </c>
-      <c r="B47" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D47" s="10" t="s">
+      <c r="B47" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E47" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F47" s="10">
+      <c r="E47" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F47" s="8">
         <v>413838009</v>
       </c>
-      <c r="G47" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="H47" s="10">
+      <c r="G47" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H47" s="8">
         <v>413838009</v>
       </c>
-      <c r="I47" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J47" s="10">
-        <v>1</v>
-      </c>
-      <c r="L47" s="10">
+      <c r="I47" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J47" s="8">
+        <v>1</v>
+      </c>
+      <c r="L47" s="8">
         <v>1</v>
       </c>
       <c r="M47"/>
@@ -3250,38 +3225,38 @@
       <c r="AF47"/>
       <c r="AG47"/>
     </row>
-    <row r="48" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="10">
+    <row r="48" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="8">
         <v>79</v>
       </c>
-      <c r="B48" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D48" s="10" t="s">
+      <c r="B48" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E48" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F48" s="10">
+      <c r="E48" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F48" s="8">
         <v>413838009</v>
       </c>
-      <c r="G48" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="H48" s="10">
+      <c r="G48" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H48" s="8">
         <v>413838009</v>
       </c>
-      <c r="I48" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J48" s="10">
-        <v>1</v>
-      </c>
-      <c r="L48" s="10">
+      <c r="I48" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J48" s="8">
+        <v>1</v>
+      </c>
+      <c r="L48" s="8">
         <v>1</v>
       </c>
       <c r="M48"/>
@@ -3306,38 +3281,38 @@
       <c r="AF48"/>
       <c r="AG48"/>
     </row>
-    <row r="49" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="11">
+    <row r="49" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="9">
         <v>85</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C49" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D49" s="10" t="s">
+      <c r="C49" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E49" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F49" s="10">
+      <c r="E49" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F49" s="8">
         <v>413838009</v>
       </c>
-      <c r="G49" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="H49" s="10">
+      <c r="G49" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H49" s="8">
         <v>413838009</v>
       </c>
-      <c r="I49" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J49" s="10">
-        <v>1</v>
-      </c>
-      <c r="L49" s="10">
+      <c r="I49" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J49" s="8">
+        <v>1</v>
+      </c>
+      <c r="L49" s="8">
         <v>1</v>
       </c>
       <c r="M49"/>
@@ -3363,109 +3338,109 @@
       <c r="AG49"/>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A50" s="10">
+      <c r="A50" s="8">
         <v>93</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" s="10" t="s">
+      <c r="C50" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E50" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F50" s="10">
+      <c r="E50" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F50" s="8">
         <v>413838009</v>
       </c>
-      <c r="G50" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="H50" s="10">
+      <c r="G50" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H50" s="8">
         <v>413838009</v>
       </c>
-      <c r="I50" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J50" s="10">
-        <v>1</v>
-      </c>
-      <c r="K50" s="10"/>
-      <c r="L50" s="10">
+      <c r="I50" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J50" s="8">
+        <v>1</v>
+      </c>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A51" s="11">
+      <c r="A51" s="9">
         <v>99</v>
       </c>
-      <c r="B51" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51" s="10" t="s">
+      <c r="B51" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E51" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F51" s="10">
+      <c r="E51" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F51" s="8">
         <v>413838009</v>
       </c>
-      <c r="G51" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="H51" s="10">
+      <c r="G51" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H51" s="8">
         <v>413838009</v>
       </c>
-      <c r="I51" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J51" s="10">
-        <v>1</v>
-      </c>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="10">
+      <c r="I51" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J51" s="8">
+        <v>1</v>
+      </c>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="8">
         <v>107</v>
       </c>
-      <c r="B52" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="10" t="s">
+      <c r="B52" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E52" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F52" s="10">
+      <c r="E52" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F52" s="8">
         <v>413838009</v>
       </c>
-      <c r="G52" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="H52" s="10">
+      <c r="G52" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H52" s="8">
         <v>413838009</v>
       </c>
-      <c r="I52" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J52" s="10">
-        <v>1</v>
-      </c>
-      <c r="L52" s="10">
+      <c r="I52" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J52" s="8">
+        <v>1</v>
+      </c>
+      <c r="L52" s="8">
         <v>1</v>
       </c>
       <c r="M52"/>
@@ -3491,110 +3466,110 @@
       <c r="AG52"/>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A53" s="11">
+      <c r="A53" s="9">
         <v>115</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C53" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="10" t="s">
+      <c r="C53" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E53" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F53" s="10">
+      <c r="E53" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F53" s="8">
         <v>413838009</v>
       </c>
-      <c r="G53" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="H53" s="10">
+      <c r="G53" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H53" s="8">
         <v>413838009</v>
       </c>
-      <c r="I53" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J53" s="10">
-        <v>1</v>
-      </c>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10">
+      <c r="I53" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J53" s="8">
+        <v>1</v>
+      </c>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A54" s="12">
+      <c r="A54" s="10">
         <v>118</v>
       </c>
-      <c r="B54" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D54" s="10" t="s">
+      <c r="B54" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E54" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F54" s="10">
+      <c r="E54" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F54" s="8">
         <v>413838009</v>
       </c>
-      <c r="G54" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="H54" s="10">
+      <c r="G54" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H54" s="8">
         <v>413838009</v>
       </c>
-      <c r="I54" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J54" s="10">
-        <v>1</v>
-      </c>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="11">
+      <c r="I54" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J54" s="8">
+        <v>1</v>
+      </c>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="9">
         <v>32</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C55" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D55" s="10" t="s">
+      <c r="C55" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E55" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F55" s="10">
+      <c r="E55" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F55" s="8">
         <v>711536002</v>
       </c>
-      <c r="G55" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="H55" s="10">
+      <c r="G55" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H55" s="8">
         <v>711536002</v>
       </c>
-      <c r="I55" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J55" s="10">
-        <v>1</v>
-      </c>
-      <c r="K55" s="12"/>
-      <c r="L55" s="10">
+      <c r="I55" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="J55" s="8">
+        <v>1</v>
+      </c>
+      <c r="K55" s="10"/>
+      <c r="L55" s="8">
         <v>1</v>
       </c>
       <c r="M55"/>
@@ -3620,216 +3595,216 @@
       <c r="AG55"/>
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A56" s="10">
+      <c r="A56" s="8">
         <v>69</v>
       </c>
-      <c r="B56" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D56" s="10" t="s">
+      <c r="B56" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E56" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F56" s="10">
+      <c r="E56" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F56" s="8">
         <v>711536002</v>
       </c>
-      <c r="G56" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="H56" s="10">
+      <c r="G56" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H56" s="8">
         <v>711536002</v>
       </c>
-      <c r="I56" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J56" s="10">
-        <v>1</v>
-      </c>
-      <c r="K56" s="10"/>
-      <c r="L56" s="10">
+      <c r="I56" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="J56" s="8">
+        <v>1</v>
+      </c>
+      <c r="K56" s="8"/>
+      <c r="L56" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A57" s="11">
+      <c r="A57" s="9">
         <v>98</v>
       </c>
-      <c r="B57" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D57" s="10" t="s">
+      <c r="B57" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E57" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F57" s="10">
+      <c r="E57" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F57" s="8">
         <v>711536002</v>
       </c>
-      <c r="G57" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="H57" s="10">
+      <c r="G57" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H57" s="8">
         <v>711536002</v>
       </c>
-      <c r="I57" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J57" s="10">
-        <v>1</v>
-      </c>
-      <c r="K57" s="10"/>
-      <c r="L57" s="10">
+      <c r="I57" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="J57" s="8">
+        <v>1</v>
+      </c>
+      <c r="K57" s="8"/>
+      <c r="L57" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A58" s="12">
+      <c r="A58" s="10">
         <v>54</v>
       </c>
-      <c r="B58" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C58" s="10" t="s">
+      <c r="B58" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C58" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D58" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="F58" s="10">
+      <c r="D58" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F58" s="8">
         <v>33367005</v>
       </c>
-      <c r="G58" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="H58" s="10">
+      <c r="G58" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H58" s="8">
         <v>33367005</v>
       </c>
-      <c r="I58" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="J58" s="10">
-        <v>1</v>
-      </c>
-      <c r="K58" s="10"/>
-      <c r="L58" s="10">
+      <c r="I58" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J58" s="8">
+        <v>1</v>
+      </c>
+      <c r="K58" s="8"/>
+      <c r="L58" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A59" s="11">
+      <c r="A59" s="9">
         <v>58</v>
       </c>
-      <c r="B59" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C59" s="10" t="s">
+      <c r="B59" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D59" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="F59" s="10">
+      <c r="D59" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F59" s="8">
         <v>33367005</v>
       </c>
-      <c r="G59" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="H59" s="10">
+      <c r="G59" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H59" s="8">
         <v>33367005</v>
       </c>
-      <c r="I59" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="J59" s="10">
-        <v>1</v>
-      </c>
-      <c r="K59" s="10"/>
-      <c r="L59" s="10">
+      <c r="I59" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J59" s="8">
+        <v>1</v>
+      </c>
+      <c r="K59" s="8"/>
+      <c r="L59" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A60" s="6">
-        <v>5</v>
-      </c>
-      <c r="B60" s="6" t="s">
+      <c r="A60" s="4">
+        <v>5</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="F60" s="6">
+      <c r="D60" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F60" s="4">
         <v>415806002</v>
       </c>
-      <c r="G60" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="H60" s="6">
+      <c r="G60" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H60" s="4">
         <v>133920001</v>
       </c>
-      <c r="I60" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="J60" s="6">
-        <v>0</v>
-      </c>
-      <c r="K60" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="L60" s="6">
+      <c r="I60" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="J60" s="4">
+        <v>0</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L60" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A61" s="7">
+      <c r="A61" s="5">
         <v>74</v>
       </c>
-      <c r="B61" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="7" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E61" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F61" s="7">
+      <c r="E61" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F61" s="5">
         <v>260678004</v>
       </c>
-      <c r="G61" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H61" s="7">
+      <c r="G61" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H61" s="5">
         <v>440678006</v>
       </c>
-      <c r="I61" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="J61" s="7">
+      <c r="I61" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J61" s="5">
         <v>0</v>
       </c>
       <c r="K61" s="1" t="s">
@@ -3843,31 +3818,31 @@
       <c r="A62" s="1">
         <v>81</v>
       </c>
-      <c r="B62" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D62" s="7" t="s">
+      <c r="B62" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E62" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F62" s="7">
+      <c r="E62" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F62" s="5">
         <v>260678004</v>
       </c>
-      <c r="G62" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H62" s="7">
+      <c r="G62" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H62" s="5">
         <v>440678006</v>
       </c>
-      <c r="I62" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="J62" s="7">
+      <c r="I62" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J62" s="5">
         <v>0</v>
       </c>
       <c r="K62" s="1" t="s">
@@ -3878,34 +3853,34 @@
       </c>
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A63" s="7">
+      <c r="A63" s="5">
         <v>87</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C63" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D63" s="7" t="s">
+      <c r="C63" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E63" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F63" s="7">
+      <c r="E63" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F63" s="5">
         <v>260678004</v>
       </c>
-      <c r="G63" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H63" s="7">
+      <c r="G63" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H63" s="5">
         <v>440678006</v>
       </c>
-      <c r="I63" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="J63" s="7">
+      <c r="I63" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J63" s="5">
         <v>0</v>
       </c>
       <c r="K63" s="1" t="s">
@@ -3929,19 +3904,19 @@
         <v>11</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F64" s="1">
         <v>260678004</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J64" s="1">
         <v>0</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L64" s="1">
         <v>0</v>
@@ -3969,40 +3944,40 @@
       <c r="AG64"/>
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A65" s="7">
+      <c r="A65" s="5">
         <v>95</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C65" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D65" s="7" t="s">
+      <c r="C65" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F65" s="7">
+      <c r="E65" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F65" s="5">
         <v>260678004</v>
       </c>
-      <c r="G65" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H65" s="7">
+      <c r="G65" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H65" s="5">
         <v>440678006</v>
       </c>
-      <c r="I65" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="J65" s="7">
-        <v>0</v>
-      </c>
-      <c r="K65" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="L65" s="7">
+      <c r="I65" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J65" s="5">
+        <v>0</v>
+      </c>
+      <c r="K65" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="L65" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4010,75 +3985,75 @@
       <c r="A66" s="1">
         <v>104</v>
       </c>
-      <c r="B66" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D66" s="7" t="s">
+      <c r="B66" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E66" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F66" s="7">
+      <c r="E66" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F66" s="5">
         <v>260678004</v>
       </c>
-      <c r="G66" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H66" s="7">
+      <c r="G66" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H66" s="5">
         <v>440678006</v>
       </c>
-      <c r="I66" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="J66" s="7">
-        <v>0</v>
-      </c>
-      <c r="K66" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="L66" s="7">
+      <c r="I66" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J66" s="5">
+        <v>0</v>
+      </c>
+      <c r="K66" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="L66" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="7">
+      <c r="A67" s="5">
         <v>109</v>
       </c>
-      <c r="B67" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67" s="7" t="s">
+      <c r="B67" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E67" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F67" s="7">
+      <c r="E67" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F67" s="5">
         <v>260678004</v>
       </c>
-      <c r="G67" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H67" s="7">
+      <c r="G67" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H67" s="5">
         <v>440678006</v>
       </c>
-      <c r="I67" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="J67" s="7">
-        <v>0</v>
-      </c>
-      <c r="K67" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="L67" s="7">
+      <c r="I67" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J67" s="5">
+        <v>0</v>
+      </c>
+      <c r="K67" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="L67" s="5">
         <v>0</v>
       </c>
       <c r="M67"/>
@@ -4104,41 +4079,41 @@
       <c r="AG67"/>
     </row>
     <row r="68" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="2">
+      <c r="A68" s="6">
         <v>25</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F68" s="2">
+      <c r="C68" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F68" s="6">
         <v>415070008</v>
       </c>
-      <c r="G68" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H68" s="2">
+      <c r="G68" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H68" s="6">
         <v>713689002</v>
       </c>
-      <c r="I68" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="J68" s="2">
-        <v>0</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="L68" s="2" t="s">
-        <v>94</v>
+      <c r="I68" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="J68" s="6">
+        <v>0</v>
+      </c>
+      <c r="K68" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L68" s="4">
+        <v>1</v>
       </c>
       <c r="M68"/>
       <c r="N68"/>
@@ -4163,40 +4138,40 @@
       <c r="AG68"/>
     </row>
     <row r="69" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="6">
+      <c r="A69" s="4">
         <v>117</v>
       </c>
-      <c r="B69" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C69" s="6" t="s">
+      <c r="B69" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C69" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D69" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F69" s="6">
+      <c r="E69" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F69" s="4">
         <v>734582004</v>
       </c>
-      <c r="G69" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="H69" s="6">
+      <c r="G69" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H69" s="4">
         <v>372525000</v>
       </c>
-      <c r="I69" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="J69" s="6">
-        <v>0</v>
-      </c>
-      <c r="K69" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="L69" s="6">
+      <c r="I69" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="J69" s="4">
+        <v>0</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L69" s="7">
         <v>1</v>
       </c>
       <c r="M69"/>
@@ -4222,83 +4197,83 @@
       <c r="AG69"/>
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A70" s="9">
+      <c r="A70" s="7">
         <v>68</v>
       </c>
-      <c r="B70" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C70" s="9" t="s">
+      <c r="B70" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D70" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E70" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="F70" s="9">
+      <c r="D70" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F70" s="7">
         <v>225773000</v>
       </c>
-      <c r="G70" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H70" s="9">
+      <c r="G70" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H70" s="7">
         <v>1156333005</v>
       </c>
-      <c r="I70" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="J70" s="9">
-        <v>0</v>
-      </c>
-      <c r="K70" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="L70" s="9">
+      <c r="I70" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="J70" s="7">
+        <v>0</v>
+      </c>
+      <c r="K70" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L70" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A71" s="3">
+      <c r="A71" s="1">
         <v>63</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C71" s="3" t="s">
+      <c r="B71" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E71" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F71" s="3">
+      <c r="E71" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F71" s="1">
         <v>840595002</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H71" s="3">
+      <c r="G71" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H71" s="1">
         <v>771452004</v>
       </c>
-      <c r="I71" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="J71" s="3">
-        <v>0</v>
-      </c>
-      <c r="K71" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L71" s="3" t="s">
-        <v>19</v>
+      <c r="I71" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J71" s="1">
+        <v>0</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L71" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A72" s="7">
+      <c r="A72" s="5">
         <v>13</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -4308,22 +4283,22 @@
         <v>5</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F72" s="1">
         <v>415070008</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H72" s="1">
         <v>713617008</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J72" s="1">
         <v>0</v>
@@ -4346,22 +4321,22 @@
         <v>5</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F73" s="1">
         <v>415070008</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H73" s="1">
         <v>713617008</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J73" s="1">
         <v>0</v>
@@ -4374,7 +4349,7 @@
       </c>
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A74" s="7">
+      <c r="A74" s="5">
         <v>53</v>
       </c>
       <c r="B74" s="1" t="s">
@@ -4384,22 +4359,22 @@
         <v>5</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F74" s="1">
         <v>415070008</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H74" s="1">
         <v>713617008</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J74" s="1">
         <v>0</v>
@@ -4416,28 +4391,28 @@
         <v>76</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F75" s="1">
         <v>415070008</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H75" s="1">
         <v>713617008</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J75" s="1">
         <v>0</v>
@@ -4450,7 +4425,7 @@
       </c>
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A76" s="7">
+      <c r="A76" s="5">
         <v>88</v>
       </c>
       <c r="B76" s="1" t="s">
@@ -4460,22 +4435,22 @@
         <v>5</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F76" s="1">
         <v>415070008</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H76" s="1">
         <v>713617008</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J76" s="1">
         <v>0</v>
@@ -4498,22 +4473,22 @@
         <v>5</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F77" s="1">
         <v>415070008</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H77" s="1">
         <v>713617008</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J77" s="1">
         <v>0</v>
@@ -4526,32 +4501,32 @@
       </c>
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A78" s="7">
+      <c r="A78" s="5">
         <v>105</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F78" s="1">
         <v>415070008</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H78" s="1">
         <v>713617008</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J78" s="1">
         <v>0</v>
@@ -4568,28 +4543,28 @@
         <v>113</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F79" s="1">
         <v>415070008</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H79" s="1">
         <v>713617008</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J79" s="1">
         <v>0</v>
@@ -4602,7 +4577,7 @@
       </c>
     </row>
     <row r="80" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A80" s="7">
+      <c r="A80" s="5">
         <v>91</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -4615,19 +4590,19 @@
         <v>11</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F80" s="1">
         <v>738956005</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H80" s="1">
         <v>13790009</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J80" s="1">
         <v>0</v>
@@ -4640,7 +4615,7 @@
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A81" s="7">
+      <c r="A81" s="5">
         <v>10</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -4653,19 +4628,19 @@
         <v>4</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F81" s="1">
         <v>1755008</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H81" s="1">
         <v>164867002</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J81" s="1">
         <v>0</v>
@@ -4691,19 +4666,19 @@
         <v>4</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F82" s="1">
         <v>1755008</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H82" s="1">
         <v>164867002</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J82" s="1">
         <v>0</v>
@@ -4716,7 +4691,7 @@
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A83" s="7">
+      <c r="A83" s="5">
         <v>17</v>
       </c>
       <c r="B83" s="1" t="s">
@@ -4726,22 +4701,22 @@
         <v>12</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F83" s="1">
         <v>275227003</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H83" s="1">
         <v>70627009</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J83" s="1">
         <v>0</v>
@@ -4764,22 +4739,22 @@
         <v>12</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F84" s="1">
         <v>275227003</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H84" s="1">
         <v>70627009</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J84" s="1">
         <v>0</v>
@@ -4792,32 +4767,32 @@
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A85" s="7">
+      <c r="A85" s="5">
         <v>57</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F85" s="1">
         <v>275227003</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H85" s="1">
         <v>70627009</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J85" s="1">
         <v>0</v>
@@ -4834,28 +4809,28 @@
         <v>61</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F86" s="1">
         <v>275227003</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H86" s="1">
         <v>70627009</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J86" s="1">
         <v>0</v>
@@ -4868,32 +4843,32 @@
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A87" s="7">
+      <c r="A87" s="5">
         <v>75</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F87" s="1">
         <v>275227003</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H87" s="1">
         <v>70627009</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J87" s="1">
         <v>0</v>
@@ -4906,7 +4881,7 @@
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A88" s="7">
+      <c r="A88" s="5">
         <v>20</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -4919,19 +4894,19 @@
         <v>4</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F88" s="1">
         <v>22298006</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H88" s="1">
         <v>164865005</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J88" s="1">
         <v>0</v>
@@ -4957,19 +4932,19 @@
         <v>4</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F89" s="1">
         <v>22298006</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H89" s="1">
         <v>164865005</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J89" s="1">
         <v>0</v>
@@ -4982,7 +4957,7 @@
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A90" s="7">
+      <c r="A90" s="5">
         <v>50</v>
       </c>
       <c r="B90" s="1" t="s">
@@ -4995,19 +4970,19 @@
         <v>4</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F90" s="1">
         <v>22298006</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H90" s="1">
         <v>164865005</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J90" s="1">
         <v>0</v>
@@ -5020,45 +4995,45 @@
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A91" s="6">
+      <c r="A91" s="4">
         <v>67</v>
       </c>
-      <c r="B91" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C91" s="6" t="s">
+      <c r="B91" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D91" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F91" s="6">
+      <c r="D91" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F91" s="4">
         <v>410596003</v>
       </c>
-      <c r="G91" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H91" s="6">
+      <c r="G91" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H91" s="4">
         <v>20481000</v>
       </c>
-      <c r="I91" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J91" s="6">
-        <v>0</v>
-      </c>
-      <c r="K91" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="L91" s="6">
+      <c r="I91" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J91" s="4">
+        <v>0</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L91" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A92" s="7">
+      <c r="A92" s="5">
         <v>49</v>
       </c>
       <c r="B92" s="1" t="s">
@@ -5071,19 +5046,19 @@
         <v>4</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F92" s="1">
         <v>52988006</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H92" s="1">
         <v>7870007</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J92" s="1">
         <v>0</v>
@@ -5100,28 +5075,28 @@
         <v>66</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F93" s="1">
         <v>250908004</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H93" s="1">
         <v>46258004</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J93" s="1">
         <v>0</v>
@@ -5134,78 +5109,78 @@
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A94" s="8">
+      <c r="A94" s="6">
         <v>55</v>
       </c>
-      <c r="B94" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C94" s="6" t="s">
+      <c r="B94" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D94" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E94" s="6" t="s">
+      <c r="D94" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F94" s="4">
+        <v>371789009</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H94" s="4">
+        <v>431558000</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J94" s="4">
+        <v>0</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L94" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A95" s="4">
+        <v>59</v>
+      </c>
+      <c r="B95" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F94" s="6">
+      <c r="C95" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F95" s="4">
         <v>371789009</v>
       </c>
-      <c r="G94" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="H94" s="6">
+      <c r="G95" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H95" s="4">
         <v>431558000</v>
       </c>
-      <c r="I94" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J94" s="6">
-        <v>0</v>
-      </c>
-      <c r="K94" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="L94" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A95" s="6">
-        <v>59</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F95" s="6">
-        <v>371789009</v>
-      </c>
-      <c r="G95" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="H95" s="6">
-        <v>431558000</v>
-      </c>
-      <c r="I95" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J95" s="6">
-        <v>0</v>
-      </c>
-      <c r="K95" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="L95" s="6">
+      <c r="I95" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J95" s="4">
+        <v>0</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L95" s="4">
         <v>1</v>
       </c>
     </row>
@@ -5214,7 +5189,7 @@
         <v>72</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>5</v>
@@ -5223,19 +5198,19 @@
         <v>4</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F96" s="1">
         <v>230165009</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H96" s="1">
         <v>1363183004</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J96" s="1">
         <v>0</v>
@@ -5252,7 +5227,7 @@
         <v>80</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>5</v>
@@ -5261,19 +5236,19 @@
         <v>4</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F97" s="1">
         <v>230165009</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H97" s="1">
         <v>1363183004</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J97" s="1">
         <v>0</v>
@@ -5299,19 +5274,19 @@
         <v>4</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F98" s="1">
         <v>230165009</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H98" s="1">
         <v>1363183004</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J98" s="1">
         <v>0</v>
@@ -5337,27 +5312,27 @@
         <v>4</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F99" s="1">
         <v>230165009</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H99" s="1">
         <v>1363183004</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J99" s="1">
         <v>0</v>
       </c>
-      <c r="K99" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="L99" s="7">
+      <c r="K99" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="L99" s="5">
         <v>0</v>
       </c>
     </row>
@@ -5366,7 +5341,7 @@
         <v>102</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>5</v>
@@ -5375,19 +5350,19 @@
         <v>4</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F100" s="1">
         <v>230165009</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H100" s="1">
         <v>1363183004</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J100" s="1">
         <v>0</v>
@@ -5404,7 +5379,7 @@
         <v>108</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>5</v>
@@ -5413,137 +5388,137 @@
         <v>4</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F101" s="1">
         <v>230165009</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H101" s="1">
         <v>1363183004</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J101" s="1">
         <v>0</v>
       </c>
-      <c r="K101" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="L101" s="7">
+      <c r="K101" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="L101" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A102" s="7">
+      <c r="A102" s="5">
         <v>111</v>
       </c>
-      <c r="B102" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D102" s="7" t="s">
+      <c r="B102" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D102" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E102" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F102" s="7">
+      <c r="E102" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F102" s="5">
         <v>230165009</v>
       </c>
-      <c r="G102" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="H102" s="7"/>
-      <c r="I102" s="7"/>
-      <c r="J102" s="7">
-        <v>0</v>
-      </c>
-      <c r="K102" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="L102" s="7">
+      <c r="G102" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H102" s="5"/>
+      <c r="I102" s="5"/>
+      <c r="J102" s="5">
+        <v>0</v>
+      </c>
+      <c r="K102" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L102" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A103" s="3">
+      <c r="A103" s="1">
         <v>65</v>
       </c>
-      <c r="B103" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C103" s="3" t="s">
+      <c r="B103" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D103" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F103" s="3">
+      <c r="D103" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F103" s="1">
         <v>363789004</v>
       </c>
-      <c r="G103" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H103" s="3">
+      <c r="G103" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H103" s="1">
         <v>7922000</v>
       </c>
-      <c r="I103" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J103" s="3">
-        <v>0</v>
-      </c>
-      <c r="K103" s="3" t="s">
+      <c r="I103" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L103" s="3" t="s">
-        <v>19</v>
+      <c r="J103" s="1">
+        <v>0</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L103" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A104" s="6">
+      <c r="A104" s="4">
         <v>120</v>
       </c>
-      <c r="B104" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D104" s="6" t="s">
+      <c r="B104" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E104" s="6" t="s">
+      <c r="C104" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F104" s="6">
+      <c r="E104" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F104" s="4">
         <v>74474003</v>
       </c>
-      <c r="G104" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H104" s="6">
+      <c r="G104" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H104" s="4">
         <v>155837004</v>
       </c>
-      <c r="I104" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J104" s="6">
-        <v>0</v>
-      </c>
-      <c r="K104" s="6" t="s">
+      <c r="I104" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="L104" s="6">
+      <c r="J104" s="4">
+        <v>0</v>
+      </c>
+      <c r="K104" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L104" s="4">
         <v>1</v>
       </c>
     </row>
@@ -5552,28 +5527,28 @@
         <v>82</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F105" s="1">
         <v>1255670000</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H105" s="1">
         <v>48696000</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J105" s="1">
         <v>0</v>
@@ -5599,13 +5574,13 @@
         <v>11</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F106" s="1">
         <v>1290126002</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H106" s="1"/>
       <c r="I106" s="1"/>
@@ -5613,7 +5588,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L106" s="1">
         <v>0</v>
@@ -5633,13 +5608,13 @@
         <v>11</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F107" s="1">
         <v>1290126002</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
@@ -5647,7 +5622,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L107" s="1">
         <v>0</v>
@@ -5667,23 +5642,23 @@
         <v>11</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F108" s="1">
         <v>1290126002</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
       <c r="J108" s="1">
         <v>0</v>
       </c>
-      <c r="K108" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="L108" s="4">
+      <c r="K108" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L108" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5692,7 +5667,7 @@
         <v>62</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>12</v>
@@ -5701,23 +5676,23 @@
         <v>11</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F109" s="1">
         <v>1290126002</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
       <c r="J109" s="1">
         <v>0</v>
       </c>
-      <c r="K109" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="L109" s="4">
+      <c r="K109" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L109" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5726,7 +5701,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>5</v>
@@ -5735,13 +5710,13 @@
         <v>11</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F110" s="1">
         <v>1290126002</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
@@ -5749,7 +5724,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L110" s="1">
         <v>0</v>
@@ -5760,28 +5735,28 @@
         <v>64</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F111" s="1">
         <v>41801008</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H111" s="1">
         <v>294002</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J111" s="1">
         <v>0</v>
@@ -5794,79 +5769,79 @@
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A112" s="3">
+      <c r="A112" s="1">
         <v>12</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B112" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E112" s="2" t="s">
+      <c r="C112" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D112" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F112" s="2">
+      <c r="E112" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F112" s="5">
         <v>232717009</v>
       </c>
-      <c r="G112" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H112" s="2">
+      <c r="G112" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H112" s="5">
         <v>232719007</v>
       </c>
-      <c r="I112" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J112" s="2">
-        <v>0</v>
-      </c>
-      <c r="K112" s="2" t="s">
+      <c r="I112" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L112" s="3">
+      <c r="J112" s="5">
+        <v>0</v>
+      </c>
+      <c r="K112" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L112" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A113" s="3">
+      <c r="A113" s="1">
         <v>33</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C113" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D113" s="3" t="s">
+      <c r="C113" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E113" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F113" s="3">
+      <c r="E113" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F113" s="1">
         <v>1366501001</v>
       </c>
-      <c r="G113" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H113" s="3">
+      <c r="G113" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H113" s="1">
         <v>1366498001</v>
       </c>
-      <c r="I113" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J113" s="3">
-        <v>0</v>
-      </c>
-      <c r="K113" s="2" t="s">
+      <c r="I113" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L113" s="2" t="s">
+      <c r="J113" s="1">
+        <v>0</v>
+      </c>
+      <c r="K113" s="5" t="s">
         <v>19</v>
+      </c>
+      <c r="L113" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.2">
